--- a/src/test/resources/caldata.xlsx
+++ b/src/test/resources/caldata.xlsx
@@ -12,7 +12,25 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
+  <si>
+    <t>Year</t>
+  </si>
+  <si>
+    <t>Principal</t>
+  </si>
+  <si>
+    <t>Interest</t>
+  </si>
+  <si>
+    <t>Total Payment</t>
+  </si>
+  <si>
+    <t>Balance</t>
+  </si>
+  <si>
+    <t>Loan Paid To Date</t>
+  </si>
   <si>
     <t>2026</t>
   </si>
@@ -89,7 +107,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -117,19 +135,39 @@
         <v>6</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2" t="s" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s" s="0">
         <v>10</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/src/test/resources/caldata.xlsx
+++ b/src/test/resources/caldata.xlsx
@@ -12,57 +12,66 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
-  <si>
-    <t>Year</t>
-  </si>
-  <si>
-    <t>Principal</t>
-  </si>
-  <si>
-    <t>Interest</t>
-  </si>
-  <si>
-    <t>Total Payment</t>
-  </si>
-  <si>
-    <t>Balance</t>
-  </si>
-  <si>
-    <t>Loan Paid To Date</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="20">
   <si>
     <t>2026</t>
   </si>
   <si>
-    <t>₹ 9,84,149</t>
+    <t>₹ 16,72,562</t>
   </si>
   <si>
-    <t>₹ 68,053</t>
+    <t>₹ 3,09,824</t>
   </si>
   <si>
-    <t>₹ 10,52,202</t>
+    <t>₹ 33,000</t>
   </si>
   <si>
-    <t>₹ 5,15,851</t>
+    <t>₹ 20,15,386</t>
   </si>
   <si>
-    <t>65.61%</t>
+    <t>₹ 36,97,438</t>
+  </si>
+  <si>
+    <t>31.15%</t>
   </si>
   <si>
     <t>2027</t>
   </si>
   <si>
-    <t>₹ 10,250</t>
+    <t>₹ 27,26,556</t>
   </si>
   <si>
-    <t>₹ 5,26,101</t>
+    <t>₹ 2,47,023</t>
+  </si>
+  <si>
+    <t>₹ 49,500</t>
+  </si>
+  <si>
+    <t>₹ 30,23,079</t>
+  </si>
+  <si>
+    <t>₹ 9,70,882</t>
+  </si>
+  <si>
+    <t>81.92%</t>
+  </si>
+  <si>
+    <t>2028</t>
+  </si>
+  <si>
+    <t>₹ 20,311</t>
+  </si>
+  <si>
+    <t>₹ 16,500</t>
+  </si>
+  <si>
+    <t>₹ 10,07,693</t>
   </si>
   <si>
     <t>₹ 0</t>
   </si>
   <si>
-    <t>100.00%</t>
+    <t>100%</t>
   </si>
 </sst>
 </file>
@@ -107,7 +116,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -129,45 +138,54 @@
       <c r="F1" t="s" s="0">
         <v>5</v>
       </c>
+      <c r="G1" t="s" s="0">
+        <v>6</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E2" t="s" s="0">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F2" t="s" s="0">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>13</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s" s="0">
         <v>12</v>
       </c>
-      <c r="B3" t="s" s="0">
-        <v>10</v>
-      </c>
       <c r="C3" t="s" s="0">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D3" t="s" s="0">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E3" t="s" s="0">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F3" t="s" s="0">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/src/test/resources/caldata.xlsx
+++ b/src/test/resources/caldata.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
   <si>
     <t>Year</t>
   </si>
@@ -23,6 +23,9 @@
     <t>Interest</t>
   </si>
   <si>
+    <t>Taxes, Home Insurance &amp; Maintenance</t>
+  </si>
+  <si>
     <t>Total Payment</t>
   </si>
   <si>
@@ -35,34 +38,61 @@
     <t>2026</t>
   </si>
   <si>
-    <t>₹ 9,84,149</t>
-  </si>
-  <si>
-    <t>₹ 68,053</t>
-  </si>
-  <si>
-    <t>₹ 10,52,202</t>
-  </si>
-  <si>
-    <t>₹ 5,15,851</t>
-  </si>
-  <si>
-    <t>65.61%</t>
+    <t>₹ 16,72,562</t>
+  </si>
+  <si>
+    <t>₹ 3,09,824</t>
+  </si>
+  <si>
+    <t>₹ 33,000</t>
+  </si>
+  <si>
+    <t>₹ 20,15,386</t>
+  </si>
+  <si>
+    <t>₹ 36,97,438</t>
+  </si>
+  <si>
+    <t>31.15%</t>
   </si>
   <si>
     <t>2027</t>
   </si>
   <si>
-    <t>₹ 10,250</t>
-  </si>
-  <si>
-    <t>₹ 5,26,101</t>
+    <t>₹ 27,26,556</t>
+  </si>
+  <si>
+    <t>₹ 2,47,023</t>
+  </si>
+  <si>
+    <t>₹ 49,500</t>
+  </si>
+  <si>
+    <t>₹ 30,23,079</t>
+  </si>
+  <si>
+    <t>₹ 9,70,882</t>
+  </si>
+  <si>
+    <t>81.92%</t>
+  </si>
+  <si>
+    <t>2028</t>
+  </si>
+  <si>
+    <t>₹ 20,311</t>
+  </si>
+  <si>
+    <t>₹ 16,500</t>
+  </si>
+  <si>
+    <t>₹ 10,07,693</t>
   </si>
   <si>
     <t>₹ 0</t>
   </si>
   <si>
-    <t>100.00%</t>
+    <t>100%</t>
   </si>
 </sst>
 </file>
@@ -107,7 +137,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -129,45 +159,77 @@
       <c r="F1" t="s" s="0">
         <v>5</v>
       </c>
+      <c r="G1" t="s" s="0">
+        <v>6</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E2" t="s" s="0">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F2" t="s" s="0">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>13</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D3" t="s" s="0">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E3" t="s" s="0">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F3" t="s" s="0">
-        <v>16</v>
+        <v>19</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
